--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7592</v>
+        <v>7617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5723</v>
+        <v>5781</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1754</v>
+        <v>1768</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1039,30 +1039,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>合肥·梦时空SPO1动漫展</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>1277</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1085,30 +1085,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1241</v>
+        <v>279</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1131,30 +1131,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>277</v>
+        <v>39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1177,43 +1177,135 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024.03.16 09:30-03.17 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>2024-04-04</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>5501</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="n">
+        <v>5515</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>合肥·梦时空SPO1动漫展</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.18 17:00</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>64</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,7 +1526,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1480,7 +1572,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7592</v>
+        <v>7617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1572,7 +1664,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1618,7 +1710,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1664,7 +1756,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1756,7 +1848,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5723</v>
+        <v>5781</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1802,7 +1894,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1848,7 +1940,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1894,7 +1986,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1940,7 +2032,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1754</v>
+        <v>1768</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1967,30 +2059,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>合肥·梦时空SPO1动漫展</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>1277</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1998,12 +2090,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -2013,30 +2105,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1241</v>
+        <v>279</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -2044,12 +2136,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2059,30 +2151,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>277</v>
+        <v>39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -2090,12 +2182,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -2105,43 +2197,135 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024.03.16 09:30-03.17 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>2024-04-04</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>5501</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="n">
+        <v>5515</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>合肥·梦时空SPO1动漫展</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.18 17:00</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>64</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
       </c>
     </row>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7617</v>
+        <v>7665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5781</v>
+        <v>5839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1768</v>
+        <v>1789</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5515</v>
+        <v>5522</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7617</v>
+        <v>7665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5781</v>
+        <v>5839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1768</v>
+        <v>1789</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5515</v>
+        <v>5522</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7665</v>
+        <v>7691</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5839</v>
+        <v>5906</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1789</v>
+        <v>1805</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1298</v>
+        <v>1316</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>247</v>
+        <v>501</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5522</v>
+        <v>5531</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7665</v>
+        <v>7691</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5839</v>
+        <v>5906</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1789</v>
+        <v>1805</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1298</v>
+        <v>1316</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>247</v>
+        <v>501</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5522</v>
+        <v>5531</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -513,15 +508,12 @@
           <t>不可售</t>
         </is>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78076</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78076</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/2v00jbxM1698999146733.jpeg</t>
         </is>
@@ -552,22 +544,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7691</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
+        <v>7768</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79566</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79566</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/iJ1Dnmla1702029064983.jpeg</t>
         </is>
@@ -605,15 +592,12 @@
           <t>已售罄</t>
         </is>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80254</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80254</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/9ClQwbVE1703668101900.jpeg</t>
         </is>
@@ -644,22 +628,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80246</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80246</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/aHzqArm61703662347629.jpeg</t>
         </is>
@@ -690,22 +671,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G6" t="n">
+        <v>65</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80917</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80917</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/UekMeUjQ1705462868391.jpeg</t>
         </is>
@@ -736,22 +712,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
         </is>
@@ -784,20 +755,15 @@
       <c r="F8" t="n">
         <v>27</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
         </is>
@@ -828,22 +794,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5906</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
+        <v>6104</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
@@ -874,22 +835,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>152</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
@@ -920,22 +876,17 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
@@ -966,22 +917,17 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
@@ -1012,22 +958,17 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1805</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>1844</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
@@ -1058,22 +999,17 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1316</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>1378</v>
+      </c>
+      <c r="G14" t="n">
+        <v>65</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
@@ -1104,22 +1040,17 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>282</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>289</v>
+      </c>
+      <c r="G15" t="n">
+        <v>68</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
@@ -1150,22 +1081,17 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>501</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>841</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
@@ -1196,22 +1122,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H17" t="b">
-        <v>1</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
@@ -1242,22 +1165,17 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5531</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>5549</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
@@ -1288,22 +1206,17 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -1320,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,15 +1272,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1384,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,15 +1331,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1448,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,15 +1390,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1533,15 +1431,12 @@
           <t>不可售</t>
         </is>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78076</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78076</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/2v00jbxM1698999146733.jpeg</t>
         </is>
@@ -1572,22 +1467,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7691</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
+        <v>7768</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79566</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79566</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/iJ1Dnmla1702029064983.jpeg</t>
         </is>
@@ -1625,15 +1515,12 @@
           <t>已售罄</t>
         </is>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80254</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80254</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/9ClQwbVE1703668101900.jpeg</t>
         </is>
@@ -1664,22 +1551,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80246</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80246</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/aHzqArm61703662347629.jpeg</t>
         </is>
@@ -1710,22 +1594,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G6" t="n">
+        <v>65</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80917</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80917</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/UekMeUjQ1705462868391.jpeg</t>
         </is>
@@ -1756,22 +1635,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
         </is>
@@ -1804,20 +1678,15 @@
       <c r="F8" t="n">
         <v>27</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
         </is>
@@ -1848,22 +1717,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5906</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
+        <v>6104</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
@@ -1894,22 +1758,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>152</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
@@ -1940,22 +1799,17 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
@@ -1986,22 +1840,17 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
@@ -2032,22 +1881,17 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1805</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>1844</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
@@ -2078,22 +1922,17 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1316</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>1378</v>
+      </c>
+      <c r="G14" t="n">
+        <v>65</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
@@ -2124,22 +1963,17 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>282</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>289</v>
+      </c>
+      <c r="G15" t="n">
+        <v>68</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
@@ -2170,22 +2004,17 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>501</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>841</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
@@ -2216,22 +2045,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H17" t="b">
-        <v>1</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
@@ -2262,22 +2088,17 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5531</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>5549</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
@@ -2308,22 +2129,17 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·SP同人展·次元派对（取消）</t>
+          <t>肥东· 原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>临泉路88号板桥里墨园E区1号省羽体中心 省羽体super速搏羽毛球馆</t>
+          <t>长江东路徽商城2幢B座(祥和地铁站C口步行370米) 曼斯顿尚品酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 17:00</t>
+          <t>2024.01.29 10:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1430</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78076</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/2v00jbxM1698999146733.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·第十二届次元之门动漫游戏博览会</t>
+          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 17:30</t>
+          <t>2024.01.31 10:00-01.31 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7768</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/iJ1Dnmla1702029064983.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,12 +564,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·第十二届次元之门动漫游戏博览会-吴磊专场</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,25 +579,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>531</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>6168</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80254</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9ClQwbVE1703668101900.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·第十二届次元之门动漫游戏博览会-赵乾景专场</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -624,25 +620,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.04 11:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>327</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>169</v>
+      </c>
+      <c r="G5" t="n">
+        <v>168</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80246</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/aHzqArm61703662347629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
       </c>
     </row>
@@ -652,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>巢湖·原神&amp;崩铁&amp;崩坏only</t>
+          <t>巢湖·原×铁×崩only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>团结东路7号 巢湖宾馆</t>
+          <t>健康东路7号 巢湖国际饭店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/UekMeUjQ1705462868391.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>肥东· 原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>长江东路徽商城2幢B座(祥和地铁站C口步行370米) 曼斯顿尚品酒店</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.29 10:00-01.29 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.31 10:00-01.31 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>1855</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>39.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6104</v>
+        <v>1388</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -816,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="G10" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>947</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -898,38 +892,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>70</v>
+        <v>200</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -939,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1844</v>
+        <v>5560</v>
       </c>
       <c r="G13" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
       </c>
     </row>
@@ -980,243 +976,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1378</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2024-02-19</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>合肥·安徽马娘only</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>289</v>
-      </c>
-      <c r="G15" t="n">
-        <v>68</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024-03-02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>841</v>
-      </c>
-      <c r="G16" t="n">
-        <v>55</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>178</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>5549</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>68</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -1351,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,40 +1194,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·SP同人展·次元派对（取消）</t>
+          <t>肥东· 原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>临泉路88号板桥里墨园E区1号省羽体中心 省羽体super速搏羽毛球馆</t>
+          <t>长江东路徽商城2幢B座(祥和地铁站C口步行370米) 曼斯顿尚品酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 17:00</t>
+          <t>2024.01.29 10:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1430</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78076</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/2v00jbxM1698999146733.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
         </is>
       </c>
     </row>
@@ -1448,38 +1235,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·第十二届次元之门动漫游戏博览会</t>
+          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 17:30</t>
+          <t>2024.01.31 10:00-01.31 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7768</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79566</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/iJ1Dnmla1702029064983.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1276,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·第十二届次元之门动漫游戏博览会-吴磊专场</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1504,25 +1291,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>531</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>6168</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80254</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9ClQwbVE1703668101900.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1317,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·第十二届次元之门动漫游戏博览会-赵乾景专场</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1547,25 +1332,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.04 11:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>327</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>169</v>
+      </c>
+      <c r="G5" t="n">
+        <v>168</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80246</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/aHzqArm61703662347629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
       </c>
     </row>
@@ -1575,38 +1358,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>巢湖·原神&amp;崩铁&amp;崩坏only</t>
+          <t>巢湖·原×铁×崩only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>团结东路7号 巢湖宾馆</t>
+          <t>健康东路7号 巢湖国际饭店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/UekMeUjQ1705462868391.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
       </c>
     </row>
@@ -1616,38 +1399,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>肥东· 原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>长江东路徽商城2幢B座(祥和地铁站C口步行370米) 曼斯顿尚品酒店</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.29 10:00-01.29 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -1657,38 +1440,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.31 10:00-01.31 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>1855</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>39.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -1698,38 +1481,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6104</v>
+        <v>1388</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1739,38 +1522,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="G10" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1780,38 +1563,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>947</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1821,38 +1604,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>70</v>
+        <v>200</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1862,38 +1647,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1844</v>
+        <v>5560</v>
       </c>
       <c r="G13" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
       </c>
     </row>
@@ -1903,243 +1688,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1378</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2024-02-19</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>合肥·安徽马娘only</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>289</v>
-      </c>
-      <c r="G15" t="n">
-        <v>68</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024-03-02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>841</v>
-      </c>
-      <c r="G16" t="n">
-        <v>55</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>178</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>5549</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>68</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6168</v>
+        <v>6204</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1855</v>
+        <v>1867</v>
       </c>
       <c r="G8" t="n">
         <v>39.9</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5560</v>
+        <v>5571</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6168</v>
+        <v>6204</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1855</v>
+        <v>1867</v>
       </c>
       <c r="G8" t="n">
         <v>39.9</v>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5560</v>
+        <v>5571</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>肥东· 原神&amp;崩铁&amp;崩坏only</t>
+          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>长江东路徽商城2幢B座(祥和地铁站C口步行370米) 曼斯顿尚品酒店</t>
+          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.29 10:00-01.29 17:00</t>
+          <t>2024.01.31 10:00-01.31 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.31 10:00-01.31 17:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>6262</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -579,23 +579,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 11:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6204</v>
+        <v>175</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>巢湖·原×铁×崩only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>健康东路7号 巢湖国际饭店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>169</v>
-      </c>
-      <c r="G5" t="n">
-        <v>168</v>
+        <v>22</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>1886</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>39.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1867</v>
+        <v>1417</v>
       </c>
       <c r="G8" t="n">
-        <v>39.9</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1399</v>
+        <v>294</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>293</v>
+        <v>955</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +853,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>951</v>
-      </c>
-      <c r="G11" t="n">
-        <v>55</v>
+        <v>240</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,40 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>215</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>5579</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,77 +937,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5571</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>70</v>
-      </c>
-      <c r="G14" t="n">
-        <v>60</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -1140,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,38 +1155,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>肥东· 原神&amp;崩铁&amp;崩坏only</t>
+          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>长江东路徽商城2幢B座(祥和地铁站C口步行370米) 曼斯顿尚品酒店</t>
+          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.29 10:00-01.29 17:00</t>
+          <t>2024.01.31 10:00-01.31 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80919</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9XumHIT31705464002179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
         </is>
       </c>
     </row>
@@ -1235,38 +1196,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.31 10:00-01.31 17:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>6262</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1237,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1291,23 +1252,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 11:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6204</v>
+        <v>175</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
       </c>
     </row>
@@ -1322,33 +1283,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>巢湖·原×铁×崩only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>健康东路7号 巢湖国际饭店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>169</v>
-      </c>
-      <c r="G5" t="n">
-        <v>168</v>
+        <v>22</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
       </c>
     </row>
@@ -1358,38 +1321,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -1399,38 +1362,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>1886</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>39.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -1440,38 +1403,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1867</v>
+        <v>1417</v>
       </c>
       <c r="G8" t="n">
-        <v>39.9</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1481,38 +1444,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1399</v>
+        <v>294</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1522,38 +1485,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>293</v>
+        <v>955</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1563,38 +1526,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>951</v>
-      </c>
-      <c r="G11" t="n">
-        <v>55</v>
+        <v>240</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1604,40 +1569,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>215</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>5579</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
       </c>
     </row>
@@ -1647,77 +1610,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5571</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>70</v>
-      </c>
-      <c r="G14" t="n">
-        <v>60</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6262</v>
+        <v>6295</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G4" t="n">
         <v>168</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1886</v>
+        <v>1898</v>
       </c>
       <c r="G7" t="n">
         <v>39.9</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5579</v>
+        <v>5586</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6262</v>
+        <v>6295</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G4" t="n">
         <v>168</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1886</v>
+        <v>1898</v>
       </c>
       <c r="G7" t="n">
         <v>39.9</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5579</v>
+        <v>5586</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6295</v>
+        <v>6363</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G4" t="n">
         <v>168</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1898</v>
+        <v>1911</v>
       </c>
       <c r="G7" t="n">
         <v>39.9</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5586</v>
+        <v>5591</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6295</v>
+        <v>6363</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G4" t="n">
         <v>168</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1898</v>
+        <v>1911</v>
       </c>
       <c r="G7" t="n">
         <v>39.9</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5586</v>
+        <v>5591</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6363</v>
+        <v>6398</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G4" t="n">
         <v>168</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1911</v>
+        <v>1917</v>
       </c>
       <c r="G7" t="n">
         <v>39.9</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1442</v>
+        <v>1453</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>964</v>
+        <v>978</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5591</v>
+        <v>5595</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6363</v>
+        <v>6398</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G4" t="n">
         <v>168</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1911</v>
+        <v>1917</v>
       </c>
       <c r="G7" t="n">
         <v>39.9</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1442</v>
+        <v>1453</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>964</v>
+        <v>978</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5591</v>
+        <v>5595</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.31 10:00-01.31 17:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>6450</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,23 +538,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 11:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6398</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,33 +569,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>巢湖·原×铁×崩only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>健康东路7号 巢湖国际饭店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>185</v>
-      </c>
-      <c r="G4" t="n">
-        <v>168</v>
+        <v>24</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,40 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>1931</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>39.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1917</v>
+        <v>1467</v>
       </c>
       <c r="G7" t="n">
-        <v>39.9</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1453</v>
+        <v>301</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>299</v>
+        <v>988</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>978</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
+        <v>323</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,40 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>291</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5595</v>
+        <v>5606</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1155,38 +1155,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>肥西·原神&amp;崩铁&amp;崩坏only</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>仙满楼·麦肯希酒店 仙满楼·麦肯希酒店</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.31 10:00-01.31 17:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>6450</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80944</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/euD63Mlp1705479140627.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1211,23 +1211,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 11:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6398</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
         </is>
       </c>
     </row>
@@ -1242,33 +1242,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>巢湖·原×铁×崩only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>健康东路7号 巢湖国际饭店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>185</v>
-      </c>
-      <c r="G4" t="n">
-        <v>168</v>
+        <v>24</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
         </is>
       </c>
     </row>
@@ -1278,40 +1280,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -1321,38 +1321,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>1931</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>39.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -1362,38 +1362,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1917</v>
+        <v>1467</v>
       </c>
       <c r="G7" t="n">
-        <v>39.9</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1403,38 +1403,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1453</v>
+        <v>301</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1444,38 +1444,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>299</v>
+        <v>988</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1485,38 +1485,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>978</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
+        <v>323</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1526,40 +1528,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>291</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5595</v>
+        <v>5606</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6450</v>
+        <v>6478</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5606</v>
+        <v>5616</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6450</v>
+        <v>6478</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5606</v>
+        <v>5616</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6478</v>
+        <v>6540</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1945</v>
+        <v>1959</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1477</v>
+        <v>1495</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5616</v>
+        <v>5623</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6478</v>
+        <v>6540</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1945</v>
+        <v>1959</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1477</v>
+        <v>1495</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5616</v>
+        <v>5623</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6540</v>
+        <v>6561</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1959</v>
+        <v>1977</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1495</v>
+        <v>1507</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5623</v>
+        <v>5627</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6540</v>
+        <v>6561</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1959</v>
+        <v>1977</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1495</v>
+        <v>1507</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5623</v>
+        <v>5627</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6561</v>
+        <v>6602</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1977</v>
+        <v>2013</v>
       </c>
       <c r="G6" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1507</v>
+        <v>1526</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5627</v>
+        <v>5631</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6561</v>
+        <v>6602</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1977</v>
+        <v>2013</v>
       </c>
       <c r="G6" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1507</v>
+        <v>1526</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5627</v>
+        <v>5631</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6602</v>
+        <v>6636</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2013</v>
+        <v>2028</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5631</v>
+        <v>5635</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6602</v>
+        <v>6636</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2013</v>
+        <v>2028</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5631</v>
+        <v>5635</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6636</v>
+        <v>6656</v>
       </c>
       <c r="G2" t="n">
         <v>75</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2028</v>
+        <v>2054</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1541</v>
+        <v>1566</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5635</v>
+        <v>5643</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6636</v>
+        <v>6656</v>
       </c>
       <c r="G2" t="n">
         <v>75</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" t="n">
         <v>168</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2028</v>
+        <v>2054</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1541</v>
+        <v>1566</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5635</v>
+        <v>5643</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6656</v>
+        <v>6673</v>
       </c>
       <c r="G2" t="n">
         <v>75</v>
@@ -542,10 +542,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
-      </c>
-      <c r="G3" t="n">
-        <v>168</v>
+        <v>191</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -626,7 +628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -667,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2054</v>
+        <v>2075</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5643</v>
+        <v>5650</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1174,7 +1176,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6656</v>
+        <v>6673</v>
       </c>
       <c r="G2" t="n">
         <v>75</v>
@@ -1215,10 +1217,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
-      </c>
-      <c r="G3" t="n">
-        <v>168</v>
+        <v>191</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1299,7 +1303,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -1340,7 +1344,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2054</v>
+        <v>2075</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1381,7 +1385,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1422,7 +1426,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -1463,7 +1467,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1504,7 +1508,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1547,7 +1551,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -1588,7 +1592,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5643</v>
+        <v>5650</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1629,7 +1633,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6673</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,40 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2109</v>
+      </c>
+      <c r="G3" t="n">
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,40 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1604</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>318</v>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,12 +646,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -665,23 +661,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2075</v>
+        <v>1030</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +687,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1580</v>
-      </c>
-      <c r="G7" t="n">
-        <v>65</v>
+        <v>489</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>313</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -773,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1021</v>
+        <v>5668</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,161 +812,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>463</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>79</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G11" t="n">
-        <v>58</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>5650</v>
-      </c>
-      <c r="G12" t="n">
-        <v>60</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>77</v>
-      </c>
-      <c r="G13" t="n">
-        <v>60</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -1103,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,38 +1030,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·六安lovelive only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.05 09:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6673</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79963</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/tBk3WVyX1702968658234.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
         </is>
       </c>
     </row>
@@ -1198,40 +1071,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华—吴晛专场</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 11:30-02.04 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2109</v>
+      </c>
+      <c r="G3" t="n">
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80551</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/MSS7qIQp1704695420767.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -1241,40 +1112,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>巢湖·原×铁×崩only</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>健康东路7号 巢湖国际饭店</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1604</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80974</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wVVrdShB1705487994232.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1284,38 +1153,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>318</v>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1194,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1340,23 +1209,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2075</v>
+        <v>1030</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1366,38 +1235,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1580</v>
-      </c>
-      <c r="G7" t="n">
-        <v>65</v>
+        <v>489</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1407,38 +1278,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>313</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1448,38 +1319,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1021</v>
+        <v>5668</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
         </is>
       </c>
     </row>
@@ -1489,161 +1360,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>463</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>79</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G11" t="n">
-        <v>58</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>5650</v>
-      </c>
-      <c r="G12" t="n">
-        <v>60</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>77</v>
-      </c>
-      <c r="G13" t="n">
-        <v>60</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -504,7 +504,7 @@
         <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2109</v>
+        <v>2133</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1604</v>
+        <v>1619</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5668</v>
+        <v>5676</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1052,7 +1052,7 @@
         <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2109</v>
+        <v>2133</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1604</v>
+        <v>1619</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5668</v>
+        <v>5676</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>2158</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2133</v>
+        <v>1644</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1619</v>
+        <v>322</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>320</v>
+        <v>1050</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1039</v>
+        <v>592</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,40 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>509</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -730,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>5723</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,77 +769,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5676</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>79</v>
-      </c>
-      <c r="G10" t="n">
-        <v>60</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -976,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,38 +987,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·六安lovelive only</t>
+          <t>合肥·新春AG动漫游戏盛典热血plus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>经开区繁华大道与莲花路交叉口 百乐门大剧院</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.05 09:00-02.05 17:00</t>
+          <t>2024.02.13 09:30-02.14 16:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>2158</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81146</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QkgtYncY1705656564257.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
         </is>
       </c>
     </row>
@@ -1071,38 +1028,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2133</v>
+        <v>1644</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1112,38 +1069,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1619</v>
+        <v>322</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1153,38 +1110,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>320</v>
+        <v>1050</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1194,38 +1151,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1039</v>
+        <v>592</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1235,40 +1192,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>509</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1278,38 +1233,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·原神&amp;星穹&amp;崩铁only</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>5723</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
         </is>
       </c>
     </row>
@@ -1319,77 +1274,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5676</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/244eBWip1700711342120.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>79</v>
-      </c>
-      <c r="G10" t="n">
-        <v>60</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2158</v>
+        <v>2174</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1644</v>
+        <v>1651</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1050</v>
+        <v>1064</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>592</v>
+        <v>633</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5723</v>
+        <v>5748</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2158</v>
+        <v>2174</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1644</v>
+        <v>1651</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1050</v>
+        <v>1064</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>592</v>
+        <v>633</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5723</v>
+        <v>5748</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2174</v>
+        <v>2205</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1651</v>
+        <v>1670</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>633</v>
+        <v>683</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5748</v>
+        <v>5765</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2174</v>
+        <v>2205</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1651</v>
+        <v>1670</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>633</v>
+        <v>683</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5748</v>
+        <v>5765</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2205</v>
+        <v>2214</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>683</v>
+        <v>717</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5765</v>
+        <v>5782</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2205</v>
+        <v>2214</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>683</v>
+        <v>717</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5765</v>
+        <v>5782</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2214</v>
+        <v>2227</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1680</v>
+        <v>1695</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5782</v>
+        <v>5803</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2214</v>
+        <v>2227</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1680</v>
+        <v>1695</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5782</v>
+        <v>5803</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2227</v>
+        <v>2234</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5803</v>
+        <v>5813</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2227</v>
+        <v>2234</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5803</v>
+        <v>5813</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2234</v>
+        <v>2266</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5813</v>
+        <v>5830</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2234</v>
+        <v>2266</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5813</v>
+        <v>5830</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2266</v>
+        <v>2271</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1708</v>
+        <v>1719</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5830</v>
+        <v>5839</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2266</v>
+        <v>2271</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1708</v>
+        <v>1719</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5830</v>
+        <v>5839</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2271</v>
+        <v>2278</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5839</v>
+        <v>5847</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2271</v>
+        <v>2278</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5839</v>
+        <v>5847</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2278</v>
+        <v>2284</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5847</v>
+        <v>5853</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2278</v>
+        <v>2284</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5847</v>
+        <v>5853</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2284</v>
+        <v>2302</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1738</v>
+        <v>1752</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>865</v>
+        <v>905</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5853</v>
+        <v>5862</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2284</v>
+        <v>2302</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1738</v>
+        <v>1752</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>865</v>
+        <v>905</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5853</v>
+        <v>5862</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>905</v>
+        <v>945</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5862</v>
+        <v>5872</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>905</v>
+        <v>945</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5862</v>
+        <v>5872</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2308</v>
+        <v>2328</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1761</v>
+        <v>1784</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>945</v>
+        <v>975</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5872</v>
+        <v>5894</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2308</v>
+        <v>2328</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1761</v>
+        <v>1784</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>945</v>
+        <v>975</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5872</v>
+        <v>5894</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2328</v>
+        <v>2335</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>975</v>
+        <v>1001</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5894</v>
+        <v>5905</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2328</v>
+        <v>2335</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>975</v>
+        <v>1001</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5894</v>
+        <v>5905</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>2345</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1793</v>
+        <v>1823</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -665,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1001</v>
+        <v>1040</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -747,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5905</v>
+        <v>5919</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1006,10 +1008,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>2345</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1047,7 +1051,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1793</v>
+        <v>1823</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1088,7 +1092,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G4" t="n">
         <v>68</v>
@@ -1129,7 +1133,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1170,7 +1174,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1001</v>
+        <v>1040</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1211,7 +1215,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1252,7 +1256,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5905</v>
+        <v>5919</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1293,7 +1297,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1040</v>
+        <v>1062</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5919</v>
+        <v>5929</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1040</v>
+        <v>1062</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5919</v>
+        <v>5929</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1832</v>
+        <v>1850</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1062</v>
+        <v>1093</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5929</v>
+        <v>5946</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1832</v>
+        <v>1850</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1062</v>
+        <v>1093</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5929</v>
+        <v>5946</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1850</v>
+        <v>1861</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1093</v>
+        <v>1117</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5946</v>
+        <v>5956</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1850</v>
+        <v>1861</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1093</v>
+        <v>1117</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5946</v>
+        <v>5956</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2344</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1880</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1861</v>
+        <v>354</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>352</v>
+        <v>1149</v>
       </c>
       <c r="G4" t="n">
-        <v>68</v>
+        <v>49.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1137</v>
+        <v>1162</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1117</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -689,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>5974</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,77 +728,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5956</v>
+        <v>98</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>98</v>
-      </c>
-      <c r="G9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -935,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,40 +946,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·新春AG动漫游戏盛典热血plus</t>
+          <t>合肥·2024运动新春动漫庆典（全ip）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.13 09:30-02.14 16:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2344</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1880</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yI94srFk1704703809648.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
         </is>
       </c>
     </row>
@@ -1032,38 +987,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1861</v>
+        <v>354</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1073,38 +1028,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>352</v>
+        <v>1149</v>
       </c>
       <c r="G4" t="n">
-        <v>68</v>
+        <v>49.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1114,38 +1069,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1137</v>
+        <v>1162</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1155,38 +1110,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1117</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1196,38 +1151,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>5974</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
         </is>
       </c>
     </row>
@@ -1237,77 +1192,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5956</v>
+        <v>98</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>98</v>
-      </c>
-      <c r="G9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1162</v>
+        <v>1185</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5974</v>
+        <v>5986</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1162</v>
+        <v>1185</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5974</v>
+        <v>5986</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1185</v>
+        <v>1225</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5986</v>
+        <v>6008</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1185</v>
+        <v>1225</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5986</v>
+        <v>6008</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1900</v>
+        <v>1912</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1225</v>
+        <v>1262</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6008</v>
+        <v>6026</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1900</v>
+        <v>1912</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1225</v>
+        <v>1262</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6008</v>
+        <v>6026</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1912</v>
+        <v>1936</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1171</v>
+        <v>1191</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1262</v>
+        <v>1327</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6026</v>
+        <v>6047</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1912</v>
+        <v>1936</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1171</v>
+        <v>1191</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1262</v>
+        <v>1327</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6026</v>
+        <v>6047</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1936</v>
+        <v>1944</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1327</v>
+        <v>1354</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6047</v>
+        <v>6066</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1936</v>
+        <v>1944</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="G4" t="n">
         <v>49.5</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1327</v>
+        <v>1354</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6047</v>
+        <v>6066</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1944</v>
+        <v>366</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.19</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>361</v>
+        <v>1223</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>49.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1207</v>
+        <v>1414</v>
       </c>
       <c r="G4" t="n">
-        <v>49.5</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1354</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>6095</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,77 +687,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6066</v>
+        <v>103</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -892,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,38 +905,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·2024运动新春动漫庆典（全ip）</t>
+          <t>合肥·安徽马娘only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>锦绣大道与清潭路交口东北角 李宁体育公园</t>
+          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.19 09:00-02.19 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1944</v>
+        <v>366</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79918</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/vzuMc0sJ1702902061660.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
         </is>
       </c>
     </row>
@@ -987,38 +946,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.19</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>361</v>
+        <v>1223</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>49.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -1028,38 +987,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1207</v>
+        <v>1414</v>
       </c>
       <c r="G4" t="n">
-        <v>49.5</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1069,38 +1028,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1354</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1110,38 +1069,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>6095</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
         </is>
       </c>
     </row>
@@ -1151,77 +1110,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6066</v>
+        <v>103</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G2" t="n">
         <v>68</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="G3" t="n">
         <v>49.5</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1414</v>
+        <v>1459</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6095</v>
+        <v>6122</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G2" t="n">
         <v>68</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="G3" t="n">
         <v>49.5</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1414</v>
+        <v>1459</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6095</v>
+        <v>6122</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G2" t="n">
         <v>68</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1232</v>
+        <v>1255</v>
       </c>
       <c r="G3" t="n">
         <v>49.5</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1459</v>
+        <v>1523</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G2" t="n">
         <v>68</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1232</v>
+        <v>1255</v>
       </c>
       <c r="G3" t="n">
         <v>49.5</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1459</v>
+        <v>1523</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6122</v>
+        <v>6152</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="G3" t="n">
         <v>49.5</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1523</v>
+        <v>1563</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6152</v>
+        <v>6177</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="G3" t="n">
         <v>49.5</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1523</v>
+        <v>1563</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6152</v>
+        <v>6177</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.19</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>374</v>
+        <v>1284</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>49.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1269</v>
+        <v>1619</v>
       </c>
       <c r="G3" t="n">
-        <v>49.5</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1563</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>6206</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6177</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
         </is>
       </c>
     </row>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -905,38 +907,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.19</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·安徽马娘only</t>
+          <t>合肥·星芒1.5动漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>桐城路与庐江路交叉口西南80米 赤阑桥文玩大厦</t>
+          <t>山西路与太原路交叉口 挥动体育</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.19 09:00-02.19 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>374</v>
+        <v>1284</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>49.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78286</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/721L5pIZ1699428443216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
         </is>
       </c>
     </row>
@@ -946,38 +948,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1269</v>
+        <v>1619</v>
       </c>
       <c r="G3" t="n">
-        <v>49.5</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -987,38 +989,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1563</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1028,38 +1030,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>6206</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
         </is>
       </c>
     </row>
@@ -1074,33 +1076,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6177</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QnupNcrS1707125949328.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1619</v>
+        <v>1658</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6206</v>
+        <v>6215</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1619</v>
+        <v>1658</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6206</v>
+        <v>6215</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1287</v>
+        <v>1306</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1658</v>
+        <v>1703</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6215</v>
+        <v>6246</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1287</v>
+        <v>1306</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1658</v>
+        <v>1703</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6215</v>
+        <v>6246</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1703</v>
+        <v>1737</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6246</v>
+        <v>6266</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1703</v>
+        <v>1737</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6246</v>
+        <v>6266</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1737</v>
+        <v>1805</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥·CW国潮动漫游戏嘉年华-赵路内场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.03.17 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81954</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/2PVn1ahm1708481741272.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6266</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -651,35 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>6287</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,36 +687,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2024.04.04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024.04.04 09:30-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>142</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2024.05.18</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>108</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F8" t="n">
+        <v>109</v>
+      </c>
+      <c r="G8" t="n">
         <v>60</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -853,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -967,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1737</v>
+        <v>1805</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -989,38 +1030,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥·CW国潮动漫游戏嘉年华-赵路内场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.03.17 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81954</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/2PVn1ahm1708481741272.jpeg</t>
         </is>
       </c>
     </row>
@@ -1030,38 +1071,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6266</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1076,35 +1117,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>6287</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
         </is>
       </c>
     </row>
@@ -1114,36 +1153,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2024.04.04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024.04.04 09:30-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>142</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2024.05.18</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>108</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F8" t="n">
+        <v>109</v>
+      </c>
+      <c r="G8" t="n">
         <v>60</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1805</v>
+        <v>1840</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6287</v>
+        <v>6302</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1805</v>
+        <v>1840</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6287</v>
+        <v>6302</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1840</v>
+        <v>1892</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6302</v>
+        <v>6316</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1840</v>
+        <v>1892</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6302</v>
+        <v>6316</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1892</v>
+        <v>1916</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6316</v>
+        <v>6329</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1892</v>
+        <v>1916</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6316</v>
+        <v>6329</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1348</v>
+        <v>1359</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1916</v>
+        <v>1977</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6329</v>
+        <v>6347</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1348</v>
+        <v>1359</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1916</v>
+        <v>1977</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6329</v>
+        <v>6347</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1977</v>
+        <v>2037</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6347</v>
+        <v>6365</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1977</v>
+        <v>2037</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6347</v>
+        <v>6365</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2037</v>
+        <v>2096</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6365</v>
+        <v>6378</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2037</v>
+        <v>2096</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6365</v>
+        <v>6378</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2096</v>
+        <v>2140</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6378</v>
+        <v>6393</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2096</v>
+        <v>2140</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6378</v>
+        <v>6393</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2140</v>
+        <v>2183</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6393</v>
+        <v>6409</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2140</v>
+        <v>2183</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6393</v>
+        <v>6409</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1379</v>
+        <v>1388</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2183</v>
+        <v>2220</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6409</v>
+        <v>6421</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1379</v>
+        <v>1388</v>
       </c>
       <c r="G2" t="n">
         <v>49.5</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2183</v>
+        <v>2220</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6409</v>
+        <v>6421</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·星芒1.5动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1388</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.5</v>
+        <v>1391</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2220</v>
+        <v>2286</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -665,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6421</v>
+        <v>6446</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -953,7 +955,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华</t>
+          <t>合肥·星芒1.5动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -967,10 +969,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1388</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.5</v>
+        <v>1391</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1008,7 +1012,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2220</v>
+        <v>2286</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1049,7 +1053,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1090,7 +1094,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1131,7 +1135,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6421</v>
+        <v>6446</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1172,7 +1176,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1215,7 +1219,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2286</v>
+        <v>2323</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6446</v>
+        <v>6472</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2286</v>
+        <v>2323</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6446</v>
+        <v>6472</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2323</v>
+        <v>2388</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6472</v>
+        <v>6493</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2323</v>
+        <v>2388</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6472</v>
+        <v>6493</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2388</v>
+        <v>2433</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6493</v>
+        <v>6517</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2388</v>
+        <v>2433</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6493</v>
+        <v>6517</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2433</v>
+        <v>2499</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6517</v>
+        <v>6538</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -732,36 +732,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2024.04.21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>合肥·银魂only</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024.04.21 09:00-04.21 17:00</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2024.05.18</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>131</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F9" t="n">
+        <v>132</v>
+      </c>
+      <c r="G9" t="n">
         <v>60</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -896,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,7 +1055,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2433</v>
+        <v>2499</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1053,7 +1096,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1135,7 +1178,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6517</v>
+        <v>6538</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1176,7 +1219,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1200,36 +1243,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2024.04.21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>合肥·银魂only</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024.04.21 09:00-04.21 17:00</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2024.05.18</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>合肥·梦时空SPO1动漫展</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>131</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F9" t="n">
+        <v>132</v>
+      </c>
+      <c r="G9" t="n">
         <v>60</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2499</v>
+        <v>2531</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6538</v>
+        <v>6549</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2499</v>
+        <v>2531</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6538</v>
+        <v>6549</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2531</v>
+        <v>2600</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6549</v>
+        <v>6581</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -732,40 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·银魂only</t>
+          <t>合肥·第二届漫画城市动漫展内场-柯暮卿</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>濉溪路118号 合肥栢景假日酒店</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.21 09:00-04.21 17:00</t>
+          <t>2024.04.04 10:00-04.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82192</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/tcAAj9aj1709193127773.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,36 +773,163 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024.04.04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>合肥·第二届漫画城市动漫展内场-风袖</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.04 17:00</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>158</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82191</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/UZiEzBcc1709192469627.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024.04.21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>合肥·银魂only</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.04.21 09:00-04.21 17:00</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>合肥·BH动漫游戏展</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024.05.03 10:00-05.04 16:00</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2024.05.18</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>合肥·梦时空SPO1动漫展（取消）</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>132</v>
-      </c>
-      <c r="G9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F12" t="n">
+        <v>134</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -939,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,7 +1180,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2531</v>
+        <v>2600</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1096,7 +1221,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1178,7 +1303,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6549</v>
+        <v>6581</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1219,7 +1344,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1243,40 +1368,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·银魂only</t>
+          <t>合肥·第二届漫画城市动漫展内场-柯暮卿</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>濉溪路118号 合肥栢景假日酒店</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.21 09:00-04.21 17:00</t>
+          <t>2024.04.04 10:00-04.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82192</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/tcAAj9aj1709193127773.jpeg</t>
         </is>
       </c>
     </row>
@@ -1286,36 +1409,163 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024.04.04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>合肥·第二届漫画城市动漫展内场-风袖</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.04 17:00</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>158</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82191</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/UZiEzBcc1709192469627.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024.04.21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>合肥·银魂only</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.04.21 09:00-04.21 17:00</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>合肥·BH动漫游戏展</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024.05.03 10:00-05.04 16:00</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2024.05.18</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>合肥·梦时空SPO1动漫展（取消）</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>132</v>
-      </c>
-      <c r="G9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F12" t="n">
+        <v>134</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2600</v>
+        <v>2641</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -566,7 +566,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6581</v>
+        <v>6603</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -689,7 +689,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2600</v>
+        <v>2641</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6581</v>
+        <v>6603</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2641</v>
+        <v>2692</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6603</v>
+        <v>6624</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>453</v>
+        <v>611</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -814,40 +814,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·银魂only</t>
+          <t>合肥· 第二届漫画城市动漫展内场-《琅声雅集》</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>濉溪路118号 合肥栢景假日酒店</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.21 09:00-04.21 17:00</t>
+          <t>2024.04.05 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82189</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZKkx4hTN1709191842946.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·BH动漫游戏展</t>
+          <t>合肥·银魂only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.05.03 10:00-05.04 16:00</t>
+          <t>2024.04.21 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
         </is>
       </c>
     </row>
@@ -898,38 +896,79 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>合肥·BH动漫游戏展</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024.05.03 10:00-05.04 16:00</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>2024-05-18</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>合肥·梦时空SPO1动漫展（取消）</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>133</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="n">
+        <v>132</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -1064,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,7 +1176,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1180,7 +1219,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2641</v>
+        <v>2692</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1221,7 +1260,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1262,7 +1301,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1303,7 +1342,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6603</v>
+        <v>6624</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1344,7 +1383,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>453</v>
+        <v>611</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1387,7 +1426,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -1428,7 +1467,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -1450,40 +1489,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥·银魂only</t>
+          <t>合肥· 第二届漫画城市动漫展内场-《琅声雅集》</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>濉溪路118号 合肥栢景假日酒店</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.21 09:00-04.21 17:00</t>
+          <t>2024.04.05 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82189</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZKkx4hTN1709191842946.jpeg</t>
         </is>
       </c>
     </row>
@@ -1493,38 +1530,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·BH动漫游戏展</t>
+          <t>合肥·银魂only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.05.03 10:00-05.04 16:00</t>
+          <t>2024.04.21 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
         </is>
       </c>
     </row>
@@ -1534,38 +1571,79 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>合肥·BH动漫游戏展</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024.05.03 10:00-05.04 16:00</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>2024-05-18</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>合肥·梦时空SPO1动漫展（取消）</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>133</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="n">
+        <v>132</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2692</v>
+        <v>2711</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6624</v>
+        <v>6632</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>611</v>
+        <v>948</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>168</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
         <v>50</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2692</v>
+        <v>2711</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="G4" t="n">
         <v>238</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6624</v>
+        <v>6632</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>611</v>
+        <v>948</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>168</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
         <v>50</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华（取消）</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1393</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2759</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,12 +523,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华-赵路内场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -540,23 +538,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.17 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2711</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>738</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81954</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/2PVn1ahm1708481741272.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华-赵路内场</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.17 09:00-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>587</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81954</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/2PVn1ahm1708481741272.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>6653</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,33 +653,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6632</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
+        <v>1309</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,35 +696,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·第二届漫画城市动漫展内场-柯暮卿</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 10:00-04.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>948</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82192</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/tcAAj9aj1709193127773.jpeg</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·第二届漫画城市动漫展内场-柯暮卿</t>
+          <t>合肥·第二届漫画城市动漫展内场-风袖</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -751,19 +751,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82191</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/tcAAj9aj1709193127773.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/UZiEzBcc1709192469627.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·第二届漫画城市动漫展内场-风袖</t>
+          <t>合肥· 第二届漫画城市动漫展内场-《琅声雅集》</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -788,23 +788,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.04 17:00</t>
+          <t>2024.04.05 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82191</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82189</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/UZiEzBcc1709192469627.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZKkx4hTN1709191842946.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +814,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展内场-《琅声雅集》</t>
+          <t>合肥·银魂only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.05 17:00</t>
+          <t>2024.04.21 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZKkx4hTN1709191842946.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·银魂only</t>
+          <t>合肥·BH动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>濉溪路118号 合肥栢景假日酒店</t>
+          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.21 09:00-04.21 17:00</t>
+          <t>2024.05.03 10:00-05.04 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,79 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合肥·BH动漫游戏展</t>
+          <t>合肥·梦时空SPO1动漫展（取消）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.05.03 10:00-05.04 16:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>40</v>
+        <v>132</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展（取消）</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>132</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>
@@ -1103,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,40 +1116,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>合肥·星芒1.5动漫嘉年华（取消）</t>
+          <t>合肥·CW国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>山西路与太原路交叉口 挥动体育</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:30</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1393</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2759</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81267</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/GWidiefU1706003134747.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1157,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华</t>
+          <t>合肥·CW国潮动漫游戏嘉年华-赵路内场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1215,23 +1172,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.17 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2711</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>738</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81954</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/38B92fWF1705995243803.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/2PVn1ahm1708481741272.jpeg</t>
         </is>
       </c>
     </row>
@@ -1241,38 +1200,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>合肥·CW国潮动漫游戏嘉年华-赵路内场</t>
+          <t>合肥·原&amp;铁&amp;崩 only展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.17 09:00-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>587</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81954</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/2PVn1ahm1708481741272.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
         </is>
       </c>
     </row>
@@ -1282,38 +1241,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>合肥·原&amp;铁&amp;崩 only展</t>
+          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金寨路与天堂窄路交叉口 梵木艺术中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>6653</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81574</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0V5uyX6C1706697212904.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
         </is>
       </c>
     </row>
@@ -1328,33 +1287,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展 -故事再次开始</t>
+          <t>合肥·环形宇宙动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6632</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
+        <v>1309</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78898</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/3NgyB9761708333056023.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
         </is>
       </c>
     </row>
@@ -1369,35 +1330,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>合肥·环形宇宙动漫游戏嘉年华</t>
+          <t>合肥·第二届漫画城市动漫展内场-柯暮卿</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京路与庐州大道交汇处 合肥滨湖国际会展中心</t>
+          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 10:00-04.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>948</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81916</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82192</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/1lGzmBT61708336972816.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/tcAAj9aj1709193127773.jpeg</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1371,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合肥·第二届漫画城市动漫展内场-柯暮卿</t>
+          <t>合肥·第二届漫画城市动漫展内场-风袖</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1426,19 +1385,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82191</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/tcAAj9aj1709193127773.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/UZiEzBcc1709192469627.jpeg</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1407,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>合肥·第二届漫画城市动漫展内场-风袖</t>
+          <t>合肥· 第二届漫画城市动漫展内场-《琅声雅集》</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1463,23 +1422,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.04 17:00</t>
+          <t>2024.04.05 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82191</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82189</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/UZiEzBcc1709192469627.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZKkx4hTN1709191842946.jpeg</t>
         </is>
       </c>
     </row>
@@ -1489,38 +1448,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合肥· 第二届漫画城市动漫展内场-《琅声雅集》</t>
+          <t>合肥·银魂only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>凤淮路与固镇路西北角 庐阳全民健身中心</t>
+          <t>濉溪路118号 合肥栢景假日酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.05 17:00</t>
+          <t>2024.04.21 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZKkx4hTN1709191842946.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
         </is>
       </c>
     </row>
@@ -1530,38 +1489,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>合肥·银魂only</t>
+          <t>合肥·BH动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>濉溪路118号 合肥栢景假日酒店</t>
+          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.21 09:00-04.21 17:00</t>
+          <t>2024.05.03 10:00-05.04 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82145</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/A0Tb5SQ51709091316985.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
         </is>
       </c>
     </row>
@@ -1571,79 +1530,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>合肥·BH动漫游戏展</t>
+          <t>合肥·梦时空SPO1动漫展（取消）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>科技园路与葡萄园路交口包河区现代农业示范园8号 圩乐田园生态营地</t>
+          <t>阜阳路16号 银瑞林国际大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.05.03 10:00-05.04 16:00</t>
+          <t>2024.05.18 10:00-05.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>40</v>
+        <v>132</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/cSR2xlY61709195356978.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>合肥·梦时空SPO1动漫展（取消）</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>阜阳路16号 银瑞林国际大酒店</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.18 17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>132</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80207</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/tQQOHYE01703574162111.jpeg</t>
         </is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2759</v>
+        <v>2791</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6653</v>
+        <v>6673</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1309</v>
+        <v>1544</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
         <v>168</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2759</v>
+        <v>2791</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6653</v>
+        <v>6673</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1309</v>
+        <v>1544</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
         <v>168</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2791</v>
+        <v>2849</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6673</v>
+        <v>6690</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1544</v>
+        <v>1586</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>168</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2791</v>
+        <v>2849</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6673</v>
+        <v>6690</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1544</v>
+        <v>1586</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>168</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/合肥-漫展信息.xlsx
+++ b/合肥-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2849</v>
+        <v>2886</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6690</v>
+        <v>6699</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1586</v>
+        <v>1615</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
         <v>168</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2849</v>
+        <v>2886</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6690</v>
+        <v>6699</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1586</v>
+        <v>1615</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
         <v>168</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
